--- a/plantillas/2_transformacion_lotes.xlsx
+++ b/plantillas/2_transformacion_lotes.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M4"/>
+  <dimension ref="A1:N4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -494,6 +494,11 @@
           <t>DIM5</t>
         </is>
       </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>COMENTARIO</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -559,6 +564,11 @@
           <t>OPR</t>
         </is>
       </c>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>Cambio a lotes reales</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -624,6 +634,11 @@
           <t>OPR</t>
         </is>
       </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>Cambio a lotes reales</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -687,6 +702,11 @@
       <c r="M4" t="inlineStr">
         <is>
           <t>OPR</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>Cambio a lotes reales</t>
         </is>
       </c>
     </row>
